--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -773,24 +773,24 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>-4.0</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>強勢股;反彈型股</t>
+          <t>強勢股;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>227</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>反彈型股</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13666,12 +13666,12 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -14355,12 +14355,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -15106,12 +15106,12 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15970,12 +15970,12 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16583,7 +16583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -16838,12 +16838,12 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -16951,12 +16951,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -17414,12 +17414,12 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -18103,12 +18103,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -18278,12 +18278,12 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18937,99 +18937,99 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>18.04</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>18.048</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>-358.57</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>31.0</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>18.04</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>18.048</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>-358.57</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD65" t="inlineStr">
         <is>
           <t>25.75</t>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19225,99 +19225,99 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>18.05</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>18.335</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>18.037</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>-199.62</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>18.335</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>18.037</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>-199.62</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD66" t="inlineStr">
         <is>
           <t>12.41</t>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>519</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -19755,7 +19755,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -19835,12 +19835,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -20411,12 +20411,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -20699,12 +20699,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -20987,12 +20987,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>192</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">

--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -11838,7 +11838,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11858,184 +11858,184 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-8.52</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>-8.52</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>-3.98</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>12.56</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>13.08</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>12.938</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>-168.36</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>7.142857142856998</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>7.509157509157466</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>-48.86</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>-3.98</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>12.56</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>13.08</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>12.938</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>-168.36</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>7.142857142856998</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>7.509157509157466</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>-48.86</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU32" t="inlineStr">
         <is>
           <t>390940.0</t>
@@ -12093,32 +12093,32 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL32" t="inlineStr">
@@ -12128,27 +12128,27 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12225,184 +12225,184 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-8.89</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>-4.02</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>13.1275</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>12.942</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>-293.40</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>-8.89</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>17.94871794871798</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>-47.13</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>-4.02</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>13.1275</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>12.942</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>-293.40</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>17.94871794871798</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>-47.13</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU33" t="inlineStr">
         <is>
           <t>549363.8</t>
@@ -12455,37 +12455,37 @@
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL33" t="inlineStr">
@@ -12495,27 +12495,27 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -12592,184 +12592,184 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-6.30</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>-6.30</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-9.0</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>-3.81</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>12.68</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>13.1825</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>12.945</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>-968.27</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>15.38461538461536</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>23.21187584345478</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>-56.01</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>12.68</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>13.1825</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>12.945</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>-968.27</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>15.38461538461536</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>23.21187584345478</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>-56.01</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU34" t="inlineStr">
         <is>
           <t>463472.6</t>
@@ -12827,32 +12827,32 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
@@ -12862,27 +12862,27 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -13194,32 +13194,32 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
@@ -13229,27 +13229,27 @@
       </c>
       <c r="BM35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="BT35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -13431,12 +13431,12 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -13561,32 +13561,32 @@
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
@@ -13596,27 +13596,27 @@
       </c>
       <c r="BM36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="BT36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13693,184 +13693,184 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>-7.04</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>-19.0</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>-3.54</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>13.27</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>12.92</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>-182.09</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>-7.04</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>2.083333333333371</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>-12.94</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>-3.54</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>12.92</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>-182.09</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>2.083333333333371</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>-12.94</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU37" t="inlineStr">
         <is>
           <t>1137975.4</t>
@@ -13923,37 +13923,37 @@
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL37" t="inlineStr">
@@ -13963,27 +13963,27 @@
       </c>
       <c r="BM37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="BT37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -14060,184 +14060,184 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>-5.93</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>-2.85</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>12.93</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>12.914</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>-112.22</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>-5.93</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>8.33333333333338</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>23.14</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>-2.85</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>12.93</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>12.914</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>-112.22</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>8.33333333333338</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
-        <is>
-          <t>23.14</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU38" t="inlineStr">
         <is>
           <t>1528723.8</t>
@@ -14290,37 +14290,37 @@
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL38" t="inlineStr">
@@ -14330,27 +14330,27 @@
       </c>
       <c r="BM38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
@@ -14365,12 +14365,12 @@
       </c>
       <c r="BT38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -14427,12 +14427,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -14657,37 +14657,37 @@
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL39" t="inlineStr">
@@ -14697,27 +14697,27 @@
       </c>
       <c r="BM39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="BT39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -14794,184 +14794,184 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>-3.70</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>13.36</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>12.891</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>-59.45</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>18.75000000000003</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>6.250000000000019</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>31.16</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>13.15</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>13.36</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>12.891</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>-59.45</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>18.75000000000003</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>6.250000000000019</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>31.16</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU40" t="inlineStr">
         <is>
           <t>1768218.0</t>
@@ -15029,32 +15029,32 @@
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
@@ -15064,27 +15064,27 @@
       </c>
       <c r="BM40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="BT40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -15161,184 +15161,184 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>-4.81</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12.35</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>-3.17</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>13.27</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>13.355</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>12.879</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>-47.21</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>6.07</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>-14.84</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-08-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12.35</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>13.355</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>12.879</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>-47.21</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>-14.84</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU41" t="inlineStr">
         <is>
           <t>1470077.0</t>
@@ -15396,32 +15396,32 @@
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71.37523111996697</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.29968367487278</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09103551034991</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="BL41" t="inlineStr">
@@ -15431,27 +15431,27 @@
       </c>
       <c r="BM41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.56%</t>
         </is>
       </c>
       <c r="BN41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工業用紙100.00% (2024年)</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="BT41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 銷售、進出口業務</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -15528,12 +15528,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-74.0</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -15633,12 +15633,12 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -15758,27 +15758,27 @@
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL42" t="inlineStr">
@@ -15798,27 +15798,27 @@
       </c>
       <c r="BM42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
@@ -15833,12 +15833,12 @@
       </c>
       <c r="BT42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>25.41</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -15895,12 +15895,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>163</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -16125,27 +16125,27 @@
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL43" t="inlineStr">
@@ -16165,27 +16165,27 @@
       </c>
       <c r="BM43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
@@ -16200,12 +16200,12 @@
       </c>
       <c r="BT43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -16262,104 +16262,104 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6.97</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
         <is>
           <t>13.05</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>0</t>
@@ -16367,12 +16367,12 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -16492,27 +16492,27 @@
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
@@ -16522,7 +16522,7 @@
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
@@ -16532,27 +16532,27 @@
       </c>
       <c r="BM44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
@@ -16567,12 +16567,12 @@
       </c>
       <c r="BT44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -16629,12 +16629,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -16734,12 +16734,12 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -16859,27 +16859,27 @@
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL45" t="inlineStr">
@@ -16899,27 +16899,27 @@
       </c>
       <c r="BM45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
@@ -16934,12 +16934,12 @@
       </c>
       <c r="BT45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-24.0</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -17101,12 +17101,12 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -17226,27 +17226,27 @@
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="BK46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL46" t="inlineStr">
@@ -17266,27 +17266,27 @@
       </c>
       <c r="BM46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="BT46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -17363,12 +17363,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -17468,12 +17468,12 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -17598,22 +17598,22 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL47" t="inlineStr">
@@ -17633,27 +17633,27 @@
       </c>
       <c r="BM47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
@@ -17668,12 +17668,12 @@
       </c>
       <c r="BT47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>20.96</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -17730,184 +17730,184 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6.97</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>12.02</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>11.9675</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>12.103</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>66.70</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>9.19</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>11.9675</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>12.103</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>66.70</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>9.19</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU48" t="inlineStr">
         <is>
           <t>19934779.4</t>
@@ -17960,27 +17960,27 @@
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL48" t="inlineStr">
@@ -18000,27 +18000,27 @@
       </c>
       <c r="BM48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
@@ -18035,12 +18035,12 @@
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -18202,12 +18202,12 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -18327,27 +18327,27 @@
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL49" t="inlineStr">
@@ -18367,27 +18367,27 @@
       </c>
       <c r="BM49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -18464,184 +18464,184 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>6.97</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>11.9575</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>12.101</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>-8.67</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>61.8518518518519</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>11.9575</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>12.101</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>-8.67</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>61.8518518518519</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU50" t="inlineStr">
         <is>
           <t>14105801.4</t>
@@ -18699,22 +18699,22 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL50" t="inlineStr">
@@ -18734,27 +18734,27 @@
       </c>
       <c r="BM50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
@@ -18769,12 +18769,12 @@
       </c>
       <c r="BT50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -18831,12 +18831,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -18936,12 +18936,12 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -19066,22 +19066,22 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.2218966521184018</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.86337647653701</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.22350748605664</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="BL51" t="inlineStr">
@@ -19101,27 +19101,27 @@
       </c>
       <c r="BM51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.93%</t>
         </is>
       </c>
       <c r="BN51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙張67.27%、紙板15.54%、紙漿12.72%、紙膠帶3.54%、其他0.75%、林木0.19% (2024年)</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
@@ -19136,12 +19136,12 @@
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、銷售、進出口業務、文化用紙</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -19303,12 +19303,12 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -19433,62 +19433,62 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="BT52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -19625,109 +19625,109 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2025-03-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2025-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>17.33</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>17.714</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>2025-03-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2025-07-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>17.44</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>17.714</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR53" t="inlineStr">
         <is>
           <t>28.57142857142819</t>
@@ -19795,67 +19795,67 @@
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
@@ -19870,12 +19870,12 @@
       </c>
       <c r="BT53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -20167,62 +20167,62 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
@@ -20237,12 +20237,12 @@
       </c>
       <c r="BT54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -20349,7 +20349,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -20404,12 +20404,12 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
@@ -20534,62 +20534,62 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
@@ -20604,12 +20604,12 @@
       </c>
       <c r="BT55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -20771,12 +20771,12 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -20896,67 +20896,67 @@
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
@@ -20971,12 +20971,12 @@
       </c>
       <c r="BT56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -21093,109 +21093,109 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>2025-03-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>2025-07-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2025-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>17.515</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>17.812</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>2025-03-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>20.25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>2025-07-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2025-07-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>17.515</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>17.812</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR57" t="inlineStr">
         <is>
           <t>41.66666666666674</t>
@@ -21268,62 +21268,62 @@
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="BT57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -21505,12 +21505,12 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -21630,67 +21630,67 @@
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR58" t="inlineStr">
@@ -21705,12 +21705,12 @@
       </c>
       <c r="BT58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -21872,12 +21872,12 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -21997,67 +21997,67 @@
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR59" t="inlineStr">
@@ -22072,12 +22072,12 @@
       </c>
       <c r="BT59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -22239,12 +22239,12 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
@@ -22369,62 +22369,62 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR60" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="BT60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -22736,62 +22736,62 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.800289590973674</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.376977068890848</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.3571879441331861</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BK61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BL61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.11</t>
         </is>
       </c>
       <c r="BM61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.75%</t>
         </is>
       </c>
       <c r="BN61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.61%</t>
         </is>
       </c>
       <c r="BO61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="BQ61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>紙器50.99%、紙板32.96%、紙張9.92%、其他6.12% (2024年)</t>
         </is>
       </c>
       <c r="BR61" t="inlineStr">
@@ -22806,12 +22806,12 @@
       </c>
       <c r="BT61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="BU61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 紙漿、紙類原料、紙器及紙類製造印刷、加工、銷售、進出口業務、文化用紙、工業用紙、家庭用紙</t>
         </is>
       </c>
     </row>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -22868,12 +22868,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -22918,7 +22918,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -22973,12 +22973,12 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -23103,22 +23103,22 @@
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="BK62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL62" t="inlineStr">
@@ -23138,27 +23138,27 @@
       </c>
       <c r="BM62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR62" t="inlineStr">
@@ -23173,12 +23173,12 @@
       </c>
       <c r="BT62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -23215,7 +23215,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -23235,104 +23235,104 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>-10.28</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2025-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
         <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>-10.28</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>2025-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-05-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
       <c r="AE63" t="inlineStr">
         <is>
           <t>0</t>
@@ -23340,12 +23340,12 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
@@ -23470,22 +23470,22 @@
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="BK63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL63" t="inlineStr">
@@ -23505,27 +23505,27 @@
       </c>
       <c r="BM63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR63" t="inlineStr">
@@ -23540,12 +23540,12 @@
       </c>
       <c r="BT63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -23602,12 +23602,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -23707,12 +23707,12 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -23832,27 +23832,27 @@
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="BK64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL64" t="inlineStr">
@@ -23872,27 +23872,27 @@
       </c>
       <c r="BM64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR64" t="inlineStr">
@@ -23907,12 +23907,12 @@
       </c>
       <c r="BT64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -23969,12 +23969,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -24074,12 +24074,12 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -24199,27 +24199,27 @@
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="BK65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL65" t="inlineStr">
@@ -24239,27 +24239,27 @@
       </c>
       <c r="BM65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR65" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -24316,7 +24316,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -24336,12 +24336,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -24441,12 +24441,12 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -24571,22 +24571,22 @@
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="BK66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL66" t="inlineStr">
@@ -24606,27 +24606,27 @@
       </c>
       <c r="BM66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR66" t="inlineStr">
@@ -24641,12 +24641,12 @@
       </c>
       <c r="BT66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24683,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -24703,184 +24703,184 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>-10.28</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>2025-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
         <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>-10.28</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>53.77999999999999</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>53.17799999999999</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>860.98</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>60.7843137254902</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>53.5947712418301</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>-39.90</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>2025-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-05-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>53.77999999999999</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>53.17799999999999</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>860.98</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>60.7843137254902</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>53.5947712418301</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>-39.90</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU67" t="inlineStr">
         <is>
           <t>16679516.6</t>
@@ -24938,22 +24938,22 @@
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="BK67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL67" t="inlineStr">
@@ -24973,27 +24973,27 @@
       </c>
       <c r="BM67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR67" t="inlineStr">
@@ -25008,12 +25008,12 @@
       </c>
       <c r="BT67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -25070,12 +25070,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
@@ -25305,22 +25305,22 @@
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="BK68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL68" t="inlineStr">
@@ -25340,27 +25340,27 @@
       </c>
       <c r="BM68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR68" t="inlineStr">
@@ -25375,12 +25375,12 @@
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -25437,12 +25437,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -25487,7 +25487,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
@@ -25667,27 +25667,27 @@
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr">
@@ -25697,7 +25697,7 @@
       </c>
       <c r="BK69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL69" t="inlineStr">
@@ -25707,27 +25707,27 @@
       </c>
       <c r="BM69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR69" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="BT69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -25804,184 +25804,184 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>-10.28</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>-10.28</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2025-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2025-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>53.88000000000001</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>52.895</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>53.14</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>209.28</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>50.98039215686276</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>60.78431372549023</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>2025-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-05-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2025-10-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>53.88000000000001</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>52.895</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>53.14</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>209.28</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AP70" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>50.98039215686276</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>60.78431372549023</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU70" t="inlineStr">
         <is>
           <t>39100702.6</t>
@@ -26039,22 +26039,22 @@
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr">
@@ -26064,7 +26064,7 @@
       </c>
       <c r="BK70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL70" t="inlineStr">
@@ -26074,27 +26074,27 @@
       </c>
       <c r="BM70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR70" t="inlineStr">
@@ -26109,12 +26109,12 @@
       </c>
       <c r="BT70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>
@@ -26151,7 +26151,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -26171,12 +26171,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -26276,12 +26276,12 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
@@ -26406,22 +26406,22 @@
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.78216123499142</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.379225178180792</t>
         </is>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.622588902528381</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="BK71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BL71" t="inlineStr">
@@ -26441,27 +26441,27 @@
       </c>
       <c r="BM71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.86%</t>
         </is>
       </c>
       <c r="BN71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-38.80%</t>
         </is>
       </c>
       <c r="BO71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="BP71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="BQ71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>租賃49.43%、商品銷售27.99%、飯店客房22.58% (2024年)</t>
         </is>
       </c>
       <c r="BR71" t="inlineStr">
@@ -26476,12 +26476,12 @@
       </c>
       <c r="BT71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BU71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 造紙 - 工業用紙</t>
         </is>
       </c>
     </row>

--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -1011,15 +1011,11 @@
           <t>38.615</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>38.729</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>39.298125</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>38.729</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>39.298125</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>38.625</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>38.75</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>39.358125</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>39.358125</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>38.6225</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>38.77</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>39.416875</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>39.416875</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>38.62</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>38.788</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>39.47625</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>38.788</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>39.47625</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>38.6075</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>38.802</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>39.534375</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>38.802</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>39.534375</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>38.59</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>38.816</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>39.59125</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>38.816</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>39.59125</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>38.57</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>38.828</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>38.828</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>39.64</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>38.5625</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>38.846</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>38.846</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>39.69</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>38.555</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>38.863</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>39.736875</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>38.863</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>39.736875</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>38.55</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>38.88399999999999</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>39.783125</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>38.88399999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>39.783125</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>9.832</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>9.9656</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>9.90325</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>9.9656</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9.90325</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>9.8635</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>9.9822</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>9.897</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>9.982200000000001</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>9.897</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>9.889</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>10.0004</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>9.891250000000001</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>10.0004</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>9.891249999999999</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>9.916</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>10.0132</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>9.885</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>10.0132</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9.885</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>9.9235</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>10.0246</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>9.8765</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>10.0246</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>9.8765</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>9.923</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>10.0346</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>9.865625</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>10.0346</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>9.865625</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>9.9175</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>10.0366</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>9.85075</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>10.0366</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>9.85075</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>9.921000000000001</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>10.0448</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>9.839125</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>10.0448</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>9.839124999999999</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>9.934999999999999</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>10.0544</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>9.8285</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>10.0544</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>9.8285</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>9.95</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>10.0714</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>9.81725</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>10.0714</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>9.81725</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>25.6875</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.369</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>24.93875</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>25.369</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>24.93875</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>25.6925</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.365</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>24.9175</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>25.365</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>24.9175</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>25.6925</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>25.366</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>24.900625</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>25.366</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>24.900625</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>25.6675</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>24.88</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>25.615</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>25.332</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>25.332</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>24.85</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>25.555</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>25.318</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>24.816875</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>25.318</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>24.816875</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>25.4975</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>25.307</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>24.776875</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>25.307</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>24.776875</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>25.45</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>24.743125</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>24.743125</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>25.4175</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>25.274</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>25.274</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24.71</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>25.3925</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>25.252</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>24.678125</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>25.252</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>24.678125</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>12.945</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>12.923</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>12.714375</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>12.923</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>12.714375</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>13.025</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>12.931</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>12.719375</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>12.931</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>12.719375</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>13.08</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>12.938</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>12.720625</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>12.938</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>12.720625</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>13.1275</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>12.942</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>12.721875</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>12.942</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>12.721875</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>13.1825</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>12.945</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>12.72125</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>12.945</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>12.72125</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>13.2075</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>12.942</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>12.71875</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>12.942</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>12.71875</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>13.235</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>12.93</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>12.71375</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>12.71375</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>13.27</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>12.92</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>12.710625</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>12.710625</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>13.31</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>12.914</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>12.70875</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>12.914</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>12.70875</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>13.3425</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>12.906</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>12.70625</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>12.906</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>12.70625</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>12.1675</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>12.174</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>12.12375</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>12.174</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>12.12375</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>12.1425</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>12.169</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>12.1175</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>12.169</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>12.1175</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>12.105</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>12.157</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>12.108125</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>12.157</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>12.108125</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>12.0875</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>12.144</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>12.10125</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>12.144</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>12.10125</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>12.055</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>12.132</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>12.093125</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>12.132</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>12.093125</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>12.0125</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>12.117</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>12.080625</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>12.117</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>12.080625</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>11.975</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>12.102</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>12.065</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>12.102</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>12.065</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>11.9675</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>12.06</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>11.9675</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>12.103</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>12.055625</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>12.103</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>12.055625</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>11.96</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>12.106</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>12.045</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>12.106</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>12.045</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>17.3825</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>17.655</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>17.915625</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>17.655</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>17.915625</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>17.4025</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>17.674</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>17.933125</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>17.674</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>17.933125</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>17.415</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>17.692</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>17.946875</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>17.692</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>17.946875</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>17.714</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>17.959375</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>17.714</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>17.959375</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>17.465</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>17.736</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>17.966875</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>17.736</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>17.966875</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>17.4825</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>17.76</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>17.973125</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>17.973125</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>17.4975</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>17.784</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>17.975625</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>17.784</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>17.975625</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>17.515</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>17.812</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>17.812</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>17.98</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>17.5425</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>17.837</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>17.980625</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>17.837</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>17.980625</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>17.5675</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>17.861</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>17.975625</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>17.861</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>17.975625</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>54.38000000000001</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>53.678</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>53.875</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>53.678</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>53.875</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>54.285</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>53.658</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>53.88125</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>53.658</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>53.88125</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>54.11499999999999</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>53.602</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>53.87125</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>53.602</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>53.87125</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>54.0</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>53.55799999999999</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>53.88625</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>53.55799999999999</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>53.88625</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>53.875</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>53.51</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>53.90124999999999</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>53.90124999999999</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>53.685</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>53.44799999999999</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>53.89624999999999</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>53.44799999999999</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>53.89624999999999</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>53.205</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>53.248</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>53.81875</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>53.248</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>53.81875</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>53.0</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>53.17799999999999</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>53.84500000000001</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>53.17799999999999</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>53.84500000000001</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>52.94</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>53.158</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>53.90124999999999</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>53.158</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>53.90124999999999</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>52.915</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>53.14599999999999</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>53.94499999999999</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>53.14599999999999</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>53.94499999999999</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>

--- a/Result/checksun/造紙工業.xlsx
+++ b/Result/checksun/造紙工業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3874,7 +3874,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>6790</t>
@@ -4299,7 +4303,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>6790</t>
@@ -8140,7 +8148,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8566,7 +8574,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8992,7 +9000,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9418,7 +9426,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9844,7 +9852,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15000,7 +15008,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15426,7 +15434,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15852,7 +15860,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16278,7 +16286,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16704,7 +16712,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17130,7 +17138,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17554,7 +17562,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>1906</t>
@@ -17976,7 +17988,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>1906</t>
@@ -18398,7 +18414,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>1906</t>
@@ -18820,7 +18840,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>1906</t>
@@ -19244,7 +19268,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -20954,7 +20978,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21382,7 +21406,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21808,7 +21832,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>1905</t>
